--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25939,7 +25939,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28181,7 +28181,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29500,7 +29500,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31215,7 +31215,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35799,7 +35799,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37118,7 +37118,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39360,7 +39360,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40679,7 +40679,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41075,7 +41075,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42394,7 +42394,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43317,7 +43317,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -43713,7 +43713,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44636,7 +44636,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45032,7 +45032,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46351,7 +46351,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47670,7 +47670,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48593,7 +48593,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49137,7 +49137,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51231,7 +51231,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52154,7 +52154,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -52698,7 +52698,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53621,7 +53621,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54165,7 +54165,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -55088,7 +55088,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55632,7 +55632,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56555,7 +56555,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57099,7 +57099,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -58022,7 +58022,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58566,7 +58566,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59489,7 +59489,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -60956,7 +60956,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61500,7 +61500,7 @@
       </c>
       <c r="AJ322" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK322" t="inlineStr">
@@ -62423,7 +62423,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62967,7 +62967,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63890,7 +63890,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -64434,7 +64434,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65357,7 +65357,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65901,7 +65901,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -66824,7 +66824,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67368,7 +67368,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68918,7 +68918,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -69462,7 +69462,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70385,7 +70385,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -70929,7 +70929,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71852,7 +71852,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -72396,7 +72396,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73319,7 +73319,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -73863,7 +73863,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -74786,7 +74786,7 @@
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
@@ -75330,7 +75330,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76253,7 +76253,7 @@
       </c>
       <c r="AJ402" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK402" t="inlineStr">
@@ -76797,7 +76797,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -77720,7 +77720,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -78264,7 +78264,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79187,7 +79187,7 @@
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -79731,7 +79731,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -80654,7 +80654,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -81198,7 +81198,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -82121,7 +82121,7 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -82665,7 +82665,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83588,7 +83588,7 @@
       </c>
       <c r="AJ442" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK442" t="inlineStr">
@@ -84132,7 +84132,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">

--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25939,7 +25939,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28181,7 +28181,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29500,7 +29500,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31215,7 +31215,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35799,7 +35799,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37118,7 +37118,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39360,7 +39360,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40679,7 +40679,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41075,7 +41075,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42394,7 +42394,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43317,7 +43317,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -43713,7 +43713,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44636,7 +44636,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45032,7 +45032,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45955,7 +45955,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46351,7 +46351,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47670,7 +47670,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48593,7 +48593,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49137,7 +49137,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51231,7 +51231,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52154,7 +52154,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -52698,7 +52698,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53621,7 +53621,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54165,7 +54165,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -55088,7 +55088,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55632,7 +55632,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56555,7 +56555,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57099,7 +57099,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -58022,7 +58022,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58566,7 +58566,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59489,7 +59489,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -60956,7 +60956,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61500,7 +61500,7 @@
       </c>
       <c r="AJ322" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK322" t="inlineStr">
@@ -62423,7 +62423,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62967,7 +62967,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63890,7 +63890,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -64434,7 +64434,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65357,7 +65357,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65901,7 +65901,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -66824,7 +66824,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67368,7 +67368,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68918,7 +68918,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -69462,7 +69462,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70385,7 +70385,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -70929,7 +70929,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71852,7 +71852,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -72396,7 +72396,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73319,7 +73319,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -73863,7 +73863,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -74786,7 +74786,7 @@
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
@@ -75330,7 +75330,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76253,7 +76253,7 @@
       </c>
       <c r="AJ402" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK402" t="inlineStr">
@@ -76797,7 +76797,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -77720,7 +77720,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -78264,7 +78264,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79187,7 +79187,7 @@
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -79731,7 +79731,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -80654,7 +80654,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -81198,7 +81198,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -82121,7 +82121,7 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -82665,7 +82665,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83588,7 +83588,7 @@
       </c>
       <c r="AJ442" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK442" t="inlineStr">
@@ -84132,7 +84132,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">

--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1705,9 +1705,6 @@
       <c r="O7" t="n">
         <v>26</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>8.172040307017268</v>
       </c>
@@ -16384,9 +16381,6 @@
       <c r="O82" t="n">
         <v>21</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>6.580246101204184</v>
       </c>
@@ -17242,9 +17236,6 @@
       <c r="O86" t="n">
         <v>28</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.05699438850552643</v>
       </c>
@@ -18561,9 +18552,6 @@
       <c r="O93" t="n">
         <v>22</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.04478130525434219</v>
       </c>
@@ -19880,9 +19868,6 @@
       <c r="O100" t="n">
         <v>49</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.09974017988467125</v>
       </c>
@@ -21199,9 +21184,6 @@
       <c r="O107" t="n">
         <v>60</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.1221308325118423</v>
       </c>
@@ -22518,9 +22500,6 @@
       <c r="O114" t="n">
         <v>51</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.103811207635066</v>
       </c>
@@ -23837,9 +23816,6 @@
       <c r="O121" t="n">
         <v>41</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.08345606888309226</v>
       </c>
@@ -25156,9 +25132,6 @@
       <c r="O128" t="n">
         <v>33</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.06717195788151328</v>
       </c>
@@ -26475,9 +26448,6 @@
       <c r="O135" t="n">
         <v>25</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.05088784687993431</v>
       </c>
@@ -27794,9 +27764,6 @@
       <c r="O142" t="n">
         <v>30</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.06106541625592116</v>
       </c>
@@ -29113,9 +29080,6 @@
       <c r="O149" t="n">
         <v>35</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.07124298563190803</v>
       </c>
@@ -30432,9 +30396,6 @@
       <c r="O156" t="n">
         <v>59</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.120095318636645</v>
       </c>
@@ -31751,9 +31712,6 @@
       <c r="O163" t="n">
         <v>29</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.0590299023807238</v>
       </c>
@@ -32839,9 +32797,6 @@
       <c r="O169" t="n">
         <v>19</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>5.921945639655841</v>
       </c>
@@ -33697,9 +33652,6 @@
       <c r="O173" t="n">
         <v>32</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.06451667599319062</v>
       </c>
@@ -35016,9 +34968,6 @@
       <c r="O180" t="n">
         <v>21</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.04233906862053135</v>
       </c>
@@ -36335,9 +36284,6 @@
       <c r="O187" t="n">
         <v>27</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.05443594536925459</v>
       </c>
@@ -37654,9 +37600,6 @@
       <c r="O194" t="n">
         <v>25</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.05040365311968018</v>
       </c>
@@ -38973,9 +38916,6 @@
       <c r="O201" t="n">
         <v>28</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.0564520914940418</v>
       </c>
@@ -40292,9 +40232,6 @@
       <c r="O208" t="n">
         <v>22</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.04435521474531856</v>
       </c>
@@ -41611,9 +41548,6 @@
       <c r="O215" t="n">
         <v>25</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.05040365311968018</v>
       </c>
@@ -42930,9 +42864,6 @@
       <c r="O222" t="n">
         <v>29</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.058468237618829</v>
       </c>
@@ -44249,9 +44180,6 @@
       <c r="O229" t="n">
         <v>31</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.06250052986840342</v>
       </c>
@@ -45568,9 +45496,6 @@
       <c r="O236" t="n">
         <v>25</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.05040365311968018</v>
       </c>
@@ -46887,9 +46812,6 @@
       <c r="O243" t="n">
         <v>9</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.01814531512308486</v>
       </c>
@@ -48206,9 +48128,6 @@
       <c r="O250" t="n">
         <v>15</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.03024219187180811</v>
       </c>
@@ -49442,9 +49361,6 @@
       <c r="O257" t="n">
         <v>16</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>4.940017382686166</v>
       </c>
@@ -50300,9 +50216,6 @@
       <c r="O261" t="n">
         <v>8</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.01597725972600457</v>
       </c>
@@ -51767,9 +51680,6 @@
       <c r="O269" t="n">
         <v>11</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.02196873212325629</v>
       </c>
@@ -53234,9 +53144,6 @@
       <c r="O277" t="n">
         <v>10</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.01997157465750572</v>
       </c>
@@ -54701,9 +54608,6 @@
       <c r="O285" t="n">
         <v>4</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.007988629863002287</v>
       </c>
@@ -56168,9 +56072,6 @@
       <c r="O293" t="n">
         <v>10</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.01997157465750572</v>
       </c>
@@ -57635,9 +57536,6 @@
       <c r="O301" t="n">
         <v>7</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.013980102260254</v>
       </c>
@@ -59102,9 +59000,6 @@
       <c r="O309" t="n">
         <v>14</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.02796020452050801</v>
       </c>
@@ -60569,9 +60464,6 @@
       <c r="O317" t="n">
         <v>11</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0.02196873212325629</v>
       </c>
@@ -62036,9 +61928,6 @@
       <c r="O325" t="n">
         <v>7</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.013980102260254</v>
       </c>
@@ -63503,9 +63392,6 @@
       <c r="O333" t="n">
         <v>10</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.01997157465750572</v>
       </c>
@@ -64970,9 +64856,6 @@
       <c r="O341" t="n">
         <v>12</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.02396588958900686</v>
       </c>
@@ -66437,9 +66320,6 @@
       <c r="O349" t="n">
         <v>13</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.02596304705475744</v>
       </c>
@@ -67673,9 +67553,6 @@
       <c r="O356" t="n">
         <v>29</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>8.854623869317965</v>
       </c>
@@ -68531,9 +68408,6 @@
       <c r="O360" t="n">
         <v>12</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.02374401318204294</v>
       </c>
@@ -69998,9 +69872,6 @@
       <c r="O368" t="n">
         <v>15</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.02968001647755368</v>
       </c>
@@ -71465,9 +71336,6 @@
       <c r="O376" t="n">
         <v>14</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0.02770134871238344</v>
       </c>
@@ -72932,9 +72800,6 @@
       <c r="O384" t="n">
         <v>16</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.03165868424272393</v>
       </c>
@@ -74399,9 +74264,6 @@
       <c r="O392" t="n">
         <v>13</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.02572268094721319</v>
       </c>
@@ -75866,9 +75728,6 @@
       <c r="O400" t="n">
         <v>10</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.01978667765170245</v>
       </c>
@@ -77333,9 +77192,6 @@
       <c r="O408" t="n">
         <v>23</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0.04550935859891565</v>
       </c>
@@ -78800,9 +78656,6 @@
       <c r="O416" t="n">
         <v>10</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.01978667765170245</v>
       </c>
@@ -80267,9 +80120,6 @@
       <c r="O424" t="n">
         <v>12</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0.02374401318204294</v>
       </c>
@@ -81734,9 +81584,6 @@
       <c r="O432" t="n">
         <v>13</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0.02572268094721319</v>
       </c>
@@ -83201,9 +83048,6 @@
       <c r="O440" t="n">
         <v>20</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0.03957335530340491</v>
       </c>
@@ -84667,9 +84511,6 @@
       </c>
       <c r="O448" t="n">
         <v>15</v>
-      </c>
-      <c r="Q448" t="n">
-        <v>0</v>
       </c>
       <c r="R448" t="n">
         <v>0.02968001647755368</v>

--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -26842,7 +26842,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28158,7 +28158,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -29474,7 +29474,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30790,7 +30790,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -32106,7 +32106,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35362,7 +35362,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36678,7 +36678,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -39310,7 +39310,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -41942,7 +41942,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43258,7 +43258,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -44574,7 +44574,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -47206,7 +47206,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48522,7 +48522,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -50610,7 +50610,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52074,7 +52074,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -53538,7 +53538,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55002,7 +55002,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -56466,7 +56466,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -57930,7 +57930,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -59394,7 +59394,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -60858,7 +60858,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -62322,7 +62322,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -63786,7 +63786,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -65250,7 +65250,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -66714,7 +66714,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -68802,7 +68802,7 @@
       </c>
       <c r="AM362" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN362" t="b">
@@ -70266,7 +70266,7 @@
       </c>
       <c r="AM370" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN370" t="b">
@@ -71730,7 +71730,7 @@
       </c>
       <c r="AM378" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN378" t="b">
@@ -73194,7 +73194,7 @@
       </c>
       <c r="AM386" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN386" t="b">
@@ -74658,7 +74658,7 @@
       </c>
       <c r="AM394" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN394" t="b">
@@ -76122,7 +76122,7 @@
       </c>
       <c r="AM402" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN402" t="b">
@@ -77586,7 +77586,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -79050,7 +79050,7 @@
       </c>
       <c r="AM418" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN418" t="b">
@@ -80514,7 +80514,7 @@
       </c>
       <c r="AM426" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN426" t="b">
@@ -81978,7 +81978,7 @@
       </c>
       <c r="AM434" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN434" t="b">
@@ -83442,7 +83442,7 @@
       </c>
       <c r="AM442" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN442" t="b">

--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34432,7 +34432,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36668,7 +36668,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37064,7 +37064,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39300,7 +39300,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40616,7 +40616,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41932,7 +41932,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42328,7 +42328,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -43644,7 +43644,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45880,7 +45880,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46276,7 +46276,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47196,7 +47196,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47592,7 +47592,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49056,7 +49056,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52064,7 +52064,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53528,7 +53528,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54072,7 +54072,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54992,7 +54992,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55536,7 +55536,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56456,7 +56456,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57000,7 +57000,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57920,7 +57920,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58464,7 +58464,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59384,7 +59384,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59928,7 +59928,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -60848,7 +60848,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61392,7 +61392,7 @@
       </c>
       <c r="AJ322" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK322" t="inlineStr">
@@ -62312,7 +62312,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62856,7 +62856,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63776,7 +63776,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -64320,7 +64320,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65784,7 +65784,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -66704,7 +66704,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67248,7 +67248,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68792,7 +68792,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -69336,7 +69336,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70256,7 +70256,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -70800,7 +70800,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71720,7 +71720,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -72264,7 +72264,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73184,7 +73184,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -73728,7 +73728,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -74648,7 +74648,7 @@
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
@@ -75192,7 +75192,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76112,7 +76112,7 @@
       </c>
       <c r="AJ402" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK402" t="inlineStr">
@@ -76656,7 +76656,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -77576,7 +77576,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -78120,7 +78120,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79040,7 +79040,7 @@
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -79584,7 +79584,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -80504,7 +80504,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -81048,7 +81048,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -81968,7 +81968,7 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -82512,7 +82512,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83432,7 +83432,7 @@
       </c>
       <c r="AJ442" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK442" t="inlineStr">
@@ -83976,7 +83976,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">

--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34432,7 +34432,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36668,7 +36668,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37064,7 +37064,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39300,7 +39300,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40616,7 +40616,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41932,7 +41932,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42328,7 +42328,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -43644,7 +43644,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45880,7 +45880,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46276,7 +46276,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47196,7 +47196,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47592,7 +47592,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49056,7 +49056,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52064,7 +52064,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53528,7 +53528,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54072,7 +54072,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54992,7 +54992,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55536,7 +55536,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56456,7 +56456,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57000,7 +57000,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57920,7 +57920,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58464,7 +58464,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59384,7 +59384,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59928,7 +59928,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -60848,7 +60848,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61392,7 +61392,7 @@
       </c>
       <c r="AJ322" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK322" t="inlineStr">
@@ -62312,7 +62312,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62856,7 +62856,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63776,7 +63776,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -64320,7 +64320,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65784,7 +65784,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -66704,7 +66704,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67248,7 +67248,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68792,7 +68792,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -69336,7 +69336,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70256,7 +70256,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -70800,7 +70800,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71720,7 +71720,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -72264,7 +72264,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73184,7 +73184,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -73728,7 +73728,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -74648,7 +74648,7 @@
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
@@ -75192,7 +75192,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76112,7 +76112,7 @@
       </c>
       <c r="AJ402" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK402" t="inlineStr">
@@ -76656,7 +76656,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -77576,7 +77576,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -78120,7 +78120,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79040,7 +79040,7 @@
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -79584,7 +79584,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -80504,7 +80504,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -81048,7 +81048,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -81968,7 +81968,7 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -82512,7 +82512,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83432,7 +83432,7 @@
       </c>
       <c r="AJ442" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK442" t="inlineStr">
@@ -83976,7 +83976,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">

--- a/diseases/d008/2010-2014.xlsx
+++ b/diseases/d008/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34432,7 +34432,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36668,7 +36668,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -37064,7 +37064,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39300,7 +39300,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40616,7 +40616,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41932,7 +41932,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42328,7 +42328,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -43644,7 +43644,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45880,7 +45880,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46276,7 +46276,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47196,7 +47196,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47592,7 +47592,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49056,7 +49056,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52064,7 +52064,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53528,7 +53528,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54072,7 +54072,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54992,7 +54992,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55536,7 +55536,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56456,7 +56456,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57000,7 +57000,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -57920,7 +57920,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58464,7 +58464,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -59384,7 +59384,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -59928,7 +59928,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -60848,7 +60848,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -61392,7 +61392,7 @@
       </c>
       <c r="AJ322" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK322" t="inlineStr">
@@ -62312,7 +62312,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -62856,7 +62856,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -63776,7 +63776,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -64320,7 +64320,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -65784,7 +65784,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -66704,7 +66704,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -67248,7 +67248,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -68792,7 +68792,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -69336,7 +69336,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -70256,7 +70256,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -70800,7 +70800,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -71720,7 +71720,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -72264,7 +72264,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -73184,7 +73184,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -73728,7 +73728,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -74648,7 +74648,7 @@
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
@@ -75192,7 +75192,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -76112,7 +76112,7 @@
       </c>
       <c r="AJ402" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK402" t="inlineStr">
@@ -76656,7 +76656,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -77576,7 +77576,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -78120,7 +78120,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -79040,7 +79040,7 @@
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -79584,7 +79584,7 @@
       </c>
       <c r="AJ421" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK421" t="inlineStr">
@@ -80504,7 +80504,7 @@
       </c>
       <c r="AJ426" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK426" t="inlineStr">
@@ -81048,7 +81048,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -81968,7 +81968,7 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -82512,7 +82512,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83432,7 +83432,7 @@
       </c>
       <c r="AJ442" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK442" t="inlineStr">
@@ -83976,7 +83976,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">
